--- a/outputs/factors/quality_regional.xlsx
+++ b/outputs/factors/quality_regional.xlsx
@@ -456,13 +456,13 @@
         <v>41333</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>0.0006464183779648977</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>-0.001347450515649929</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>-0.0003505160688425158</v>
       </c>
     </row>
     <row r="3">
@@ -470,13 +470,13 @@
         <v>41364</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>0.003730001680088621</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>-0.002274659984899758</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>0.0007276708475944316</v>
       </c>
     </row>
     <row r="4">
@@ -484,13 +484,13 @@
         <v>41394</v>
       </c>
       <c r="B4" t="n">
-        <v>0.002077935237166161</v>
+        <v>0.004584096639860199</v>
       </c>
       <c r="C4" t="n">
-        <v>2.271386509247988e-05</v>
+        <v>0.003007490360202006</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001050324551129321</v>
+        <v>0.003795793500031102</v>
       </c>
     </row>
     <row r="5">
@@ -498,13 +498,13 @@
         <v>41425</v>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>0.004440451236115791</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0001021814740453164</v>
+        <v>0.001387836365523922</v>
       </c>
       <c r="D5" t="n">
-        <v>5.109073702265818e-05</v>
+        <v>0.002914143800819856</v>
       </c>
     </row>
     <row r="6">
@@ -512,13 +512,13 @@
         <v>41455</v>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>-0.001191064545822214</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>-0.005229600484890305</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>-0.00321033251535626</v>
       </c>
     </row>
     <row r="7">
@@ -526,13 +526,13 @@
         <v>41486</v>
       </c>
       <c r="B7" t="n">
-        <v>0.002189736964030124</v>
+        <v>0.001309895662827956</v>
       </c>
       <c r="C7" t="n">
-        <v>0.002668893552896424</v>
+        <v>0.00694843448176742</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002429315258463274</v>
+        <v>0.004129165072297688</v>
       </c>
     </row>
     <row r="8">
@@ -540,13 +540,13 @@
         <v>41517</v>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>-0.00157613265994363</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>-0.0005216809093954764</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>-0.001048906784669553</v>
       </c>
     </row>
     <row r="9">
@@ -554,13 +554,13 @@
         <v>41547</v>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>0.004346640756468053</v>
       </c>
       <c r="C9" t="n">
-        <v>0.00286391512092537</v>
+        <v>0.008114738891455878</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001431957560462685</v>
+        <v>0.006230689823961966</v>
       </c>
     </row>
     <row r="10">
@@ -568,13 +568,13 @@
         <v>41578</v>
       </c>
       <c r="B10" t="n">
-        <v>0.002964769335725578</v>
+        <v>0.003340140135400725</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0005725304503832439</v>
+        <v>0.003654965561254071</v>
       </c>
       <c r="D10" t="n">
-        <v>0.001768649893054411</v>
+        <v>0.003497552848327398</v>
       </c>
     </row>
     <row r="11">
@@ -582,13 +582,13 @@
         <v>41608</v>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>0.002279148145502532</v>
       </c>
       <c r="C11" t="n">
-        <v>4.335577597186581e-05</v>
+        <v>0.00242092048517027</v>
       </c>
       <c r="D11" t="n">
-        <v>2.167788798593291e-05</v>
+        <v>0.002350034315336401</v>
       </c>
     </row>
     <row r="12">
@@ -596,13 +596,13 @@
         <v>41639</v>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>0.002176004639658104</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0007644146702312872</v>
+        <v>0.003941305216414739</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0003822073351156436</v>
+        <v>0.003058654928036421</v>
       </c>
     </row>
     <row r="13">
@@ -610,13 +610,13 @@
         <v>41670</v>
       </c>
       <c r="B13" t="n">
-        <v>-8.017919914769663e-05</v>
+        <v>0.001672290812908014</v>
       </c>
       <c r="C13" t="n">
-        <v>0.001106981067238744</v>
+        <v>0.000207255416731402</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0005134009340455237</v>
+        <v>0.0009397731148197081</v>
       </c>
     </row>
     <row r="14">
@@ -624,13 +624,13 @@
         <v>41698</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.004673792376787575</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>0.006251580088315504</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>0.00546268623255154</v>
       </c>
     </row>
     <row r="15">
@@ -638,13 +638,13 @@
         <v>41729</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>0.00124390177425936</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>0.0007316857939921801</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>0.00098779378412577</v>
       </c>
     </row>
     <row r="16">
@@ -652,13 +652,13 @@
         <v>41759</v>
       </c>
       <c r="B16" t="n">
-        <v>-0.001618833365112756</v>
+        <v>-0.001425513663682168</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.001150793750082523</v>
+        <v>0.0004490664116014787</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.00138481355759764</v>
+        <v>-0.0004882236260403448</v>
       </c>
     </row>
     <row r="17">
@@ -666,13 +666,13 @@
         <v>41790</v>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>0.002905978136828493</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>-0.0008226054965866367</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>0.001041686320120928</v>
       </c>
     </row>
     <row r="18">
@@ -680,13 +680,13 @@
         <v>41820</v>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>0.00170556159764738</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>-0.0005907481449356799</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>0.0005574067263558502</v>
       </c>
     </row>
     <row r="19">
@@ -694,13 +694,13 @@
         <v>41851</v>
       </c>
       <c r="B19" t="n">
-        <v>-0.002274672312946819</v>
+        <v>-0.002739076306872596</v>
       </c>
       <c r="C19" t="n">
-        <v>-7.713283913035627e-05</v>
+        <v>-0.003630109319772133</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.001175902576038587</v>
+        <v>-0.003184592813322364</v>
       </c>
     </row>
     <row r="20">
@@ -708,13 +708,13 @@
         <v>41882</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>0.0066570654951178</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>-0.001203863124100613</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>0.002726601185508594</v>
       </c>
     </row>
     <row r="21">
@@ -722,13 +722,13 @@
         <v>41912</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>-0.003129954355717286</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>-0.002250164651907973</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>-0.002690059503812629</v>
       </c>
     </row>
     <row r="22">
@@ -736,13 +736,13 @@
         <v>41943</v>
       </c>
       <c r="B22" t="n">
-        <v>-0.004055505899304549</v>
+        <v>0.0006911148480891861</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.00139969715577934</v>
+        <v>-0.002553232521999082</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.002727601527541945</v>
+        <v>-0.0009310588369549479</v>
       </c>
     </row>
     <row r="23">
@@ -750,13 +750,13 @@
         <v>41973</v>
       </c>
       <c r="B23" t="n">
-        <v>0.004946470938505829</v>
+        <v>0.004676231150979429</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>0.003084035366685683</v>
       </c>
       <c r="D23" t="n">
-        <v>0.002473235469252915</v>
+        <v>0.003880133258832556</v>
       </c>
     </row>
     <row r="24">
@@ -764,13 +764,13 @@
         <v>42004</v>
       </c>
       <c r="B24" t="n">
-        <v>0.0009322756480841918</v>
+        <v>0.001106806636804685</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>-0.003911732644345483</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0004661378240420959</v>
+        <v>-0.001402463003770399</v>
       </c>
     </row>
     <row r="25">
@@ -778,13 +778,13 @@
         <v>42035</v>
       </c>
       <c r="B25" t="n">
-        <v>-0.002672338873885176</v>
+        <v>-0.0005630737210391423</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.001877982615189892</v>
+        <v>-0.0003810274898671551</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.002275160744537534</v>
+        <v>-0.0004720506054531487</v>
       </c>
     </row>
     <row r="26">
@@ -792,13 +792,13 @@
         <v>42063</v>
       </c>
       <c r="B26" t="n">
-        <v>0.01180173776804409</v>
+        <v>0.005793165912723787</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>0.008094572996400182</v>
       </c>
       <c r="D26" t="n">
-        <v>0.005900868884022044</v>
+        <v>0.006943869454561985</v>
       </c>
     </row>
     <row r="27">
@@ -806,13 +806,13 @@
         <v>42094</v>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>0.0005589529443352637</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>0.0001415915412721697</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>0.0003502722428037167</v>
       </c>
     </row>
     <row r="28">
@@ -820,13 +820,13 @@
         <v>42124</v>
       </c>
       <c r="B28" t="n">
-        <v>0.001313542822973927</v>
+        <v>0.004784749419871552</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.001128763815627347</v>
+        <v>0.00411526869030365</v>
       </c>
       <c r="D28" t="n">
-        <v>9.238950367328961e-05</v>
+        <v>0.004450009055087601</v>
       </c>
     </row>
     <row r="29">
@@ -834,13 +834,13 @@
         <v>42155</v>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>0.00269749861871435</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>0.0002277512317259292</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>0.00146262492522014</v>
       </c>
     </row>
     <row r="30">
@@ -848,13 +848,13 @@
         <v>42185</v>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>-0.0004986051937094696</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>-0.003542195769374361</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>-0.002020400481541916</v>
       </c>
     </row>
     <row r="31">
@@ -862,13 +862,13 @@
         <v>42216</v>
       </c>
       <c r="B31" t="n">
-        <v>0.001145813403521837</v>
+        <v>0.002253010481910406</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0007578032636717019</v>
+        <v>-2.562023514714289e-05</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0009518083335967696</v>
+        <v>0.001113695123381632</v>
       </c>
     </row>
     <row r="32">
@@ -876,13 +876,13 @@
         <v>42247</v>
       </c>
       <c r="B32" t="n">
-        <v>0</v>
+        <v>-0.004370027262503021</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>-0.003394233513804344</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>-0.003882130388153683</v>
       </c>
     </row>
     <row r="33">
@@ -890,13 +890,13 @@
         <v>42277</v>
       </c>
       <c r="B33" t="n">
-        <v>0</v>
+        <v>-0.002089923302924358</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>-0.004397495917532425</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>-0.003243709610228391</v>
       </c>
     </row>
     <row r="34">
@@ -904,13 +904,13 @@
         <v>42308</v>
       </c>
       <c r="B34" t="n">
-        <v>0.003041149215766573</v>
+        <v>0.007186666922745805</v>
       </c>
       <c r="C34" t="n">
-        <v>0.0009219619452871943</v>
+        <v>0.003318837288575152</v>
       </c>
       <c r="D34" t="n">
-        <v>0.001981555580526884</v>
+        <v>0.005252752105660478</v>
       </c>
     </row>
     <row r="35">
@@ -918,13 +918,13 @@
         <v>42338</v>
       </c>
       <c r="B35" t="n">
-        <v>0</v>
+        <v>-0.0003722821632993212</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>-0.0005041882344482901</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>-0.0004382351988738057</v>
       </c>
     </row>
     <row r="36">
@@ -932,13 +932,13 @@
         <v>42369</v>
       </c>
       <c r="B36" t="n">
-        <v>0</v>
+        <v>-0.002229522623106698</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>-0.002928389736199182</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>-0.00257895617965294</v>
       </c>
     </row>
     <row r="37">
@@ -946,13 +946,13 @@
         <v>42400</v>
       </c>
       <c r="B37" t="n">
-        <v>-0.003821311387723408</v>
+        <v>-0.01237985799814532</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.00176165140687365</v>
+        <v>-0.006530412927347492</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.002791481397298529</v>
+        <v>-0.009455135462746405</v>
       </c>
     </row>
     <row r="38">
@@ -960,13 +960,13 @@
         <v>42429</v>
       </c>
       <c r="B38" t="n">
-        <v>0</v>
+        <v>0.002389413628600961</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>0.000827920151624618</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>0.001608666890112789</v>
       </c>
     </row>
     <row r="39">
@@ -974,13 +974,13 @@
         <v>42460</v>
       </c>
       <c r="B39" t="n">
-        <v>0</v>
+        <v>0.007994215406088336</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>0.008740260647929944</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>0.008367238027009141</v>
       </c>
     </row>
     <row r="40">
@@ -988,13 +988,13 @@
         <v>42490</v>
       </c>
       <c r="B40" t="n">
-        <v>-5.265347627472486e-05</v>
+        <v>0.0002290762991657145</v>
       </c>
       <c r="C40" t="n">
-        <v>0.0005129785540515354</v>
+        <v>0.003779127164324725</v>
       </c>
       <c r="D40" t="n">
-        <v>0.0002301625388884053</v>
+        <v>0.002004101731745219</v>
       </c>
     </row>
     <row r="41">
@@ -1002,13 +1002,13 @@
         <v>42521</v>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>0.002762382461413073</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>-0.001175209733257241</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>0.0007935863640779158</v>
       </c>
     </row>
     <row r="42">
@@ -1016,13 +1016,13 @@
         <v>42551</v>
       </c>
       <c r="B42" t="n">
-        <v>0</v>
+        <v>-0.002177093725220763</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>-0.007214228328584015</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>-0.004695661026902389</v>
       </c>
     </row>
     <row r="43">
@@ -1030,13 +1030,13 @@
         <v>42582</v>
       </c>
       <c r="B43" t="n">
-        <v>0.003276053367953493</v>
+        <v>0.008062102416822939</v>
       </c>
       <c r="C43" t="n">
-        <v>0.001866854789954349</v>
+        <v>0.00433623726878219</v>
       </c>
       <c r="D43" t="n">
-        <v>0.002571454078953921</v>
+        <v>0.006199169842802565</v>
       </c>
     </row>
     <row r="44">
@@ -1044,13 +1044,13 @@
         <v>42613</v>
       </c>
       <c r="B44" t="n">
-        <v>0</v>
+        <v>0.003459109367903988</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>0.002155825573984711</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>0.00280746747094435</v>
       </c>
     </row>
     <row r="45">
@@ -1058,13 +1058,13 @@
         <v>42643</v>
       </c>
       <c r="B45" t="n">
-        <v>0</v>
+        <v>0.0002805220269787154</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>0.001467452546271549</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>0.0008739872866251324</v>
       </c>
     </row>
     <row r="46">
@@ -1072,13 +1072,13 @@
         <v>42674</v>
       </c>
       <c r="B46" t="n">
-        <v>-0.001038940735963466</v>
+        <v>-0.005425288699310207</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.0006992601555054139</v>
+        <v>0.002283270809813332</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.0008691004457344398</v>
+        <v>-0.001571008944748438</v>
       </c>
     </row>
     <row r="47">
@@ -1086,13 +1086,13 @@
         <v>42704</v>
       </c>
       <c r="B47" t="n">
-        <v>0</v>
+        <v>0.006632817458218565</v>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>-0.0002402200233175296</v>
       </c>
       <c r="D47" t="n">
-        <v>0</v>
+        <v>0.003196298717450518</v>
       </c>
     </row>
     <row r="48">
@@ -1100,13 +1100,13 @@
         <v>42735</v>
       </c>
       <c r="B48" t="n">
-        <v>0</v>
+        <v>0.002790664400104195</v>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>0.005169210669722369</v>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>0.003979937534913282</v>
       </c>
     </row>
     <row r="49">
@@ -1114,13 +1114,13 @@
         <v>42766</v>
       </c>
       <c r="B49" t="n">
-        <v>0.002962472767911108</v>
+        <v>0.00627442042698195</v>
       </c>
       <c r="C49" t="n">
-        <v>0.0003668879362606011</v>
+        <v>0.00315646227833137</v>
       </c>
       <c r="D49" t="n">
-        <v>0.001664680352085855</v>
+        <v>0.00471544135265666</v>
       </c>
     </row>
     <row r="50">
@@ -1128,13 +1128,13 @@
         <v>42794</v>
       </c>
       <c r="B50" t="n">
-        <v>0.001365488738131738</v>
+        <v>0.00941217325692229</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.0001140008641563373</v>
+        <v>0.0009219027783444149</v>
       </c>
       <c r="D50" t="n">
-        <v>0.0006257439369877003</v>
+        <v>0.005167038017633353</v>
       </c>
     </row>
     <row r="51">
@@ -1142,13 +1142,13 @@
         <v>42825</v>
       </c>
       <c r="B51" t="n">
-        <v>0</v>
+        <v>-0.001199347159126169</v>
       </c>
       <c r="C51" t="n">
-        <v>0</v>
+        <v>0.005568527383242665</v>
       </c>
       <c r="D51" t="n">
-        <v>0</v>
+        <v>0.002184590112058248</v>
       </c>
     </row>
     <row r="52">
@@ -1156,13 +1156,13 @@
         <v>42855</v>
       </c>
       <c r="B52" t="n">
-        <v>0.0008036135360031139</v>
+        <v>0.001342414974385815</v>
       </c>
       <c r="C52" t="n">
-        <v>0.0006516848641511796</v>
+        <v>0.002558683287438116</v>
       </c>
       <c r="D52" t="n">
-        <v>0.0007276492000771467</v>
+        <v>0.001950549130911966</v>
       </c>
     </row>
     <row r="53">
@@ -1170,13 +1170,13 @@
         <v>42886</v>
       </c>
       <c r="B53" t="n">
-        <v>0.0009432583361033925</v>
+        <v>0.002347631039943142</v>
       </c>
       <c r="C53" t="n">
-        <v>2.099539593151091e-05</v>
+        <v>0.005061382967035795</v>
       </c>
       <c r="D53" t="n">
-        <v>0.0004821268660174517</v>
+        <v>0.003704507003489468</v>
       </c>
     </row>
     <row r="54">
@@ -1184,13 +1184,13 @@
         <v>42916</v>
       </c>
       <c r="B54" t="n">
-        <v>0</v>
+        <v>0.001321239802399088</v>
       </c>
       <c r="C54" t="n">
-        <v>0</v>
+        <v>-8.310659837339092e-05</v>
       </c>
       <c r="D54" t="n">
-        <v>0</v>
+        <v>0.0006190666020128486</v>
       </c>
     </row>
     <row r="55">
@@ -1198,13 +1198,13 @@
         <v>42947</v>
       </c>
       <c r="B55" t="n">
-        <v>0.001059184929712604</v>
+        <v>0.003484908555884556</v>
       </c>
       <c r="C55" t="n">
-        <v>0.0006061359036098089</v>
+        <v>0.006268078721937012</v>
       </c>
       <c r="D55" t="n">
-        <v>0.0008326604166612064</v>
+        <v>0.004876493638910784</v>
       </c>
     </row>
     <row r="56">
@@ -1212,13 +1212,13 @@
         <v>42978</v>
       </c>
       <c r="B56" t="n">
-        <v>0.0006875101118277388</v>
+        <v>0.0009015909306951407</v>
       </c>
       <c r="C56" t="n">
-        <v>0</v>
+        <v>0.001110742654041702</v>
       </c>
       <c r="D56" t="n">
-        <v>0.0003437550559138694</v>
+        <v>0.001006166792368421</v>
       </c>
     </row>
     <row r="57">
@@ -1226,13 +1226,13 @@
         <v>43008</v>
       </c>
       <c r="B57" t="n">
-        <v>0.001892235092545656</v>
+        <v>0.003700091206803687</v>
       </c>
       <c r="C57" t="n">
-        <v>0</v>
+        <v>0.004558851920699106</v>
       </c>
       <c r="D57" t="n">
-        <v>0.0009461175462728278</v>
+        <v>0.004129471563751397</v>
       </c>
     </row>
     <row r="58">
@@ -1240,13 +1240,13 @@
         <v>43039</v>
       </c>
       <c r="B58" t="n">
-        <v>0.001760836940515907</v>
+        <v>0.0002486518471176917</v>
       </c>
       <c r="C58" t="n">
-        <v>6.782911736555132e-05</v>
+        <v>0.00105591761225357</v>
       </c>
       <c r="D58" t="n">
-        <v>0.0009143330289407293</v>
+        <v>0.0006522847296856309</v>
       </c>
     </row>
     <row r="59">
@@ -1254,13 +1254,13 @@
         <v>43069</v>
       </c>
       <c r="B59" t="n">
-        <v>0.005022319619867602</v>
+        <v>0.003039992350213648</v>
       </c>
       <c r="C59" t="n">
-        <v>0.0003618127917457707</v>
+        <v>2.93130323077719e-05</v>
       </c>
       <c r="D59" t="n">
-        <v>0.002692066205806687</v>
+        <v>0.00153465269126071</v>
       </c>
     </row>
     <row r="60">
@@ -1268,13 +1268,13 @@
         <v>43100</v>
       </c>
       <c r="B60" t="n">
-        <v>-3.978993472639388e-05</v>
+        <v>-0.0007498833465334534</v>
       </c>
       <c r="C60" t="n">
-        <v>2.773073591562918e-05</v>
+        <v>0.00150650996869144</v>
       </c>
       <c r="D60" t="n">
-        <v>-6.029599405382353e-06</v>
+        <v>0.0003783133110789932</v>
       </c>
     </row>
     <row r="61">
@@ -1282,13 +1282,13 @@
         <v>43131</v>
       </c>
       <c r="B61" t="n">
-        <v>0.002346170844973213</v>
+        <v>0.006583695928289746</v>
       </c>
       <c r="C61" t="n">
-        <v>0.0007643884671317933</v>
+        <v>0.002647888968189333</v>
       </c>
       <c r="D61" t="n">
-        <v>0.001555279656052503</v>
+        <v>0.00461579244823954</v>
       </c>
     </row>
     <row r="62">
@@ -1296,13 +1296,13 @@
         <v>43159</v>
       </c>
       <c r="B62" t="n">
-        <v>0</v>
+        <v>-0.001642628620705529</v>
       </c>
       <c r="C62" t="n">
-        <v>0</v>
+        <v>-0.004291168222351832</v>
       </c>
       <c r="D62" t="n">
-        <v>0</v>
+        <v>-0.00296689842152868</v>
       </c>
     </row>
     <row r="63">
@@ -1310,13 +1310,13 @@
         <v>43190</v>
       </c>
       <c r="B63" t="n">
-        <v>0</v>
+        <v>-0.003307243027745681</v>
       </c>
       <c r="C63" t="n">
-        <v>0</v>
+        <v>-0.00158406303172889</v>
       </c>
       <c r="D63" t="n">
-        <v>0</v>
+        <v>-0.002445653029737285</v>
       </c>
     </row>
     <row r="64">
@@ -1324,13 +1324,13 @@
         <v>43220</v>
       </c>
       <c r="B64" t="n">
-        <v>-0.001107134896535168</v>
+        <v>-0.001318422557983088</v>
       </c>
       <c r="C64" t="n">
-        <v>-7.492610274300575e-05</v>
+        <v>0.001529956217221693</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.0005910304996390869</v>
+        <v>0.0001057668296193021</v>
       </c>
     </row>
     <row r="65">
@@ -1338,13 +1338,13 @@
         <v>43251</v>
       </c>
       <c r="B65" t="n">
-        <v>0</v>
+        <v>0.001775707124169035</v>
       </c>
       <c r="C65" t="n">
-        <v>0</v>
+        <v>-0.004162998040219668</v>
       </c>
       <c r="D65" t="n">
-        <v>0</v>
+        <v>-0.001193645458025317</v>
       </c>
     </row>
     <row r="66">
@@ -1352,13 +1352,13 @@
         <v>43281</v>
       </c>
       <c r="B66" t="n">
-        <v>0</v>
+        <v>0.0004434912535664662</v>
       </c>
       <c r="C66" t="n">
-        <v>0</v>
+        <v>0.0005643786459948059</v>
       </c>
       <c r="D66" t="n">
-        <v>0</v>
+        <v>0.000503934949780636</v>
       </c>
     </row>
     <row r="67">
@@ -1366,13 +1366,13 @@
         <v>43312</v>
       </c>
       <c r="B67" t="n">
-        <v>0.001653608897384688</v>
+        <v>-0.0007759622970615191</v>
       </c>
       <c r="C67" t="n">
-        <v>5.447462358106884e-05</v>
+        <v>0.002164930835421046</v>
       </c>
       <c r="D67" t="n">
-        <v>0.0008540417604828783</v>
+        <v>0.0006944842691797634</v>
       </c>
     </row>
     <row r="68">
@@ -1380,13 +1380,13 @@
         <v>43343</v>
       </c>
       <c r="B68" t="n">
-        <v>0</v>
+        <v>0.001971615072699751</v>
       </c>
       <c r="C68" t="n">
-        <v>0</v>
+        <v>-0.003120256977851017</v>
       </c>
       <c r="D68" t="n">
-        <v>0</v>
+        <v>-0.0005743209525756331</v>
       </c>
     </row>
     <row r="69">
@@ -1394,13 +1394,13 @@
         <v>43373</v>
       </c>
       <c r="B69" t="n">
-        <v>0</v>
+        <v>0.001649963066796615</v>
       </c>
       <c r="C69" t="n">
-        <v>0</v>
+        <v>-0.0007133854555666539</v>
       </c>
       <c r="D69" t="n">
-        <v>0</v>
+        <v>0.0004682888056149804</v>
       </c>
     </row>
     <row r="70">
@@ -1408,13 +1408,13 @@
         <v>43404</v>
       </c>
       <c r="B70" t="n">
-        <v>-0.002660788675178948</v>
+        <v>-0.009753100733163749</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.000191165794037651</v>
+        <v>-0.005343944139591806</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.0014259772346083</v>
+        <v>-0.007548522436377778</v>
       </c>
     </row>
     <row r="71">
@@ -1422,13 +1422,13 @@
         <v>43434</v>
       </c>
       <c r="B71" t="n">
-        <v>0</v>
+        <v>0.001939468976410948</v>
       </c>
       <c r="C71" t="n">
-        <v>0</v>
+        <v>-0.00346295495778946</v>
       </c>
       <c r="D71" t="n">
-        <v>0</v>
+        <v>-0.0007617429906892563</v>
       </c>
     </row>
     <row r="72">
@@ -1436,13 +1436,13 @@
         <v>43465</v>
       </c>
       <c r="B72" t="n">
-        <v>0</v>
+        <v>-0.008421263217160847</v>
       </c>
       <c r="C72" t="n">
-        <v>0</v>
+        <v>-0.005511014462212119</v>
       </c>
       <c r="D72" t="n">
-        <v>0</v>
+        <v>-0.006966138839686483</v>
       </c>
     </row>
     <row r="73">
@@ -1450,13 +1450,13 @@
         <v>43496</v>
       </c>
       <c r="B73" t="n">
-        <v>0.003632560382519536</v>
+        <v>0.01247640309558165</v>
       </c>
       <c r="C73" t="n">
-        <v>0.001756901531014429</v>
+        <v>0.007017608871916958</v>
       </c>
       <c r="D73" t="n">
-        <v>0.002694730956766983</v>
+        <v>0.009747005983749306</v>
       </c>
     </row>
     <row r="74">
@@ -1464,13 +1464,13 @@
         <v>43524</v>
       </c>
       <c r="B74" t="n">
-        <v>0</v>
+        <v>0.005679279699250118</v>
       </c>
       <c r="C74" t="n">
-        <v>0</v>
+        <v>0.005683420369755509</v>
       </c>
       <c r="D74" t="n">
-        <v>0</v>
+        <v>0.005681350034502814</v>
       </c>
     </row>
     <row r="75">
@@ -1478,13 +1478,13 @@
         <v>43555</v>
       </c>
       <c r="B75" t="n">
-        <v>0.00235521809136211</v>
+        <v>0.0002645373696722055</v>
       </c>
       <c r="C75" t="n">
-        <v>0</v>
+        <v>-0.001525449251993815</v>
       </c>
       <c r="D75" t="n">
-        <v>0.001177609045681055</v>
+        <v>-0.000630455941160805</v>
       </c>
     </row>
     <row r="76">
@@ -1492,13 +1492,13 @@
         <v>43585</v>
       </c>
       <c r="B76" t="n">
-        <v>0.001687135343522177</v>
+        <v>0.003913586545832789</v>
       </c>
       <c r="C76" t="n">
-        <v>0.001120119145685863</v>
+        <v>0.002869727263644807</v>
       </c>
       <c r="D76" t="n">
-        <v>0.00140362724460402</v>
+        <v>0.003391656904738798</v>
       </c>
     </row>
     <row r="77">
@@ -1506,13 +1506,13 @@
         <v>43616</v>
       </c>
       <c r="B77" t="n">
-        <v>0</v>
+        <v>-0.00511043739103892</v>
       </c>
       <c r="C77" t="n">
-        <v>0</v>
+        <v>-0.009725659504987202</v>
       </c>
       <c r="D77" t="n">
-        <v>0</v>
+        <v>-0.007418048448013061</v>
       </c>
     </row>
     <row r="78">
@@ -1520,13 +1520,13 @@
         <v>43646</v>
       </c>
       <c r="B78" t="n">
-        <v>0</v>
+        <v>0.006065721444462647</v>
       </c>
       <c r="C78" t="n">
-        <v>0</v>
+        <v>0.007728938647811209</v>
       </c>
       <c r="D78" t="n">
-        <v>0</v>
+        <v>0.006897330046136928</v>
       </c>
     </row>
     <row r="79">
@@ -1534,13 +1534,13 @@
         <v>43677</v>
       </c>
       <c r="B79" t="n">
-        <v>0.00061124992010959</v>
+        <v>0.00178924468614245</v>
       </c>
       <c r="C79" t="n">
-        <v>-0.0001084103175787965</v>
+        <v>0.003439300061520085</v>
       </c>
       <c r="D79" t="n">
-        <v>0.0002514198012653968</v>
+        <v>0.002614272373831268</v>
       </c>
     </row>
     <row r="80">
@@ -1548,13 +1548,13 @@
         <v>43708</v>
       </c>
       <c r="B80" t="n">
-        <v>0</v>
+        <v>-0.003155204748136695</v>
       </c>
       <c r="C80" t="n">
-        <v>0</v>
+        <v>-0.004859699390455967</v>
       </c>
       <c r="D80" t="n">
-        <v>0</v>
+        <v>-0.004007452069296331</v>
       </c>
     </row>
     <row r="81">
@@ -1562,13 +1562,13 @@
         <v>43738</v>
       </c>
       <c r="B81" t="n">
-        <v>0</v>
+        <v>0.003829013730208154</v>
       </c>
       <c r="C81" t="n">
-        <v>0</v>
+        <v>0.005532546609327877</v>
       </c>
       <c r="D81" t="n">
-        <v>0</v>
+        <v>0.004680780169768015</v>
       </c>
     </row>
     <row r="82">
@@ -1576,13 +1576,13 @@
         <v>43769</v>
       </c>
       <c r="B82" t="n">
-        <v>0.0008142864768281515</v>
+        <v>0.001516320471012023</v>
       </c>
       <c r="C82" t="n">
-        <v>0.0009918487959652601</v>
+        <v>0.003158785306874112</v>
       </c>
       <c r="D82" t="n">
-        <v>0.0009030676363967058</v>
+        <v>0.002337552888943068</v>
       </c>
     </row>
     <row r="83">
@@ -1590,13 +1590,13 @@
         <v>43799</v>
       </c>
       <c r="B83" t="n">
-        <v>0</v>
+        <v>0.006036314147655873</v>
       </c>
       <c r="C83" t="n">
-        <v>0</v>
+        <v>0.002015076198260158</v>
       </c>
       <c r="D83" t="n">
-        <v>0</v>
+        <v>0.004025695172958015</v>
       </c>
     </row>
     <row r="84">
@@ -1604,13 +1604,13 @@
         <v>43830</v>
       </c>
       <c r="B84" t="n">
-        <v>0</v>
+        <v>0.003084197727777267</v>
       </c>
       <c r="C84" t="n">
-        <v>0</v>
+        <v>0.003127123737673212</v>
       </c>
       <c r="D84" t="n">
-        <v>0</v>
+        <v>0.00310566073272524</v>
       </c>
     </row>
     <row r="85">
@@ -1618,13 +1618,13 @@
         <v>43861</v>
       </c>
       <c r="B85" t="n">
-        <v>0.0007518906838848817</v>
+        <v>0.002333144925729654</v>
       </c>
       <c r="C85" t="n">
-        <v>-0.0006813820517180271</v>
+        <v>-0.001539739791946345</v>
       </c>
       <c r="D85" t="n">
-        <v>3.525431608342731e-05</v>
+        <v>0.0003967025668916547</v>
       </c>
     </row>
     <row r="86">
@@ -1632,13 +1632,13 @@
         <v>43890</v>
       </c>
       <c r="B86" t="n">
-        <v>0</v>
+        <v>-0.007829237373336085</v>
       </c>
       <c r="C86" t="n">
-        <v>0</v>
+        <v>-0.01189013702607641</v>
       </c>
       <c r="D86" t="n">
-        <v>0</v>
+        <v>-0.009859687199706247</v>
       </c>
     </row>
     <row r="87">
@@ -1646,13 +1646,13 @@
         <v>43921</v>
       </c>
       <c r="B87" t="n">
-        <v>0</v>
+        <v>-0.01349756731076036</v>
       </c>
       <c r="C87" t="n">
-        <v>0</v>
+        <v>-0.02036451711882695</v>
       </c>
       <c r="D87" t="n">
-        <v>0</v>
+        <v>-0.01693104221479366</v>
       </c>
     </row>
     <row r="88">
@@ -1660,13 +1660,13 @@
         <v>43951</v>
       </c>
       <c r="B88" t="n">
-        <v>0.004978079122996888</v>
+        <v>0.02518292223887024</v>
       </c>
       <c r="C88" t="n">
-        <v>-0.0001560232391405308</v>
+        <v>0.009513182347542445</v>
       </c>
       <c r="D88" t="n">
-        <v>0.002411027941928178</v>
+        <v>0.01734805229320634</v>
       </c>
     </row>
     <row r="89">
@@ -1674,13 +1674,13 @@
         <v>43982</v>
       </c>
       <c r="B89" t="n">
-        <v>0</v>
+        <v>0.007157665629085601</v>
       </c>
       <c r="C89" t="n">
-        <v>0</v>
+        <v>0.006479436273451668</v>
       </c>
       <c r="D89" t="n">
-        <v>0</v>
+        <v>0.006818550951268635</v>
       </c>
     </row>
     <row r="90">
@@ -1688,13 +1688,13 @@
         <v>44012</v>
       </c>
       <c r="B90" t="n">
-        <v>0.004367691900719442</v>
+        <v>0.006179559856849878</v>
       </c>
       <c r="C90" t="n">
-        <v>0.006201755030174</v>
+        <v>0.005383337416582247</v>
       </c>
       <c r="D90" t="n">
-        <v>0.005284723465446721</v>
+        <v>0.005781448636716062</v>
       </c>
     </row>
     <row r="91">
@@ -1702,13 +1702,13 @@
         <v>44043</v>
       </c>
       <c r="B91" t="n">
-        <v>0.008276804270241092</v>
+        <v>0.00377917878754297</v>
       </c>
       <c r="C91" t="n">
-        <v>0.0007420493396032086</v>
+        <v>0.006201863873446157</v>
       </c>
       <c r="D91" t="n">
-        <v>0.00450942680492215</v>
+        <v>0.004990521330494564</v>
       </c>
     </row>
     <row r="92">
@@ -1716,13 +1716,13 @@
         <v>44074</v>
       </c>
       <c r="B92" t="n">
-        <v>0</v>
+        <v>0.00331954735638937</v>
       </c>
       <c r="C92" t="n">
-        <v>0</v>
+        <v>0.005657195909227033</v>
       </c>
       <c r="D92" t="n">
-        <v>0</v>
+        <v>0.004488371632808201</v>
       </c>
     </row>
     <row r="93">
@@ -1730,13 +1730,13 @@
         <v>44104</v>
       </c>
       <c r="B93" t="n">
-        <v>0</v>
+        <v>-0.00182279803781938</v>
       </c>
       <c r="C93" t="n">
-        <v>0</v>
+        <v>-0.003271766973402883</v>
       </c>
       <c r="D93" t="n">
-        <v>0</v>
+        <v>-0.002547282505611131</v>
       </c>
     </row>
     <row r="94">
@@ -1744,13 +1744,13 @@
         <v>44135</v>
       </c>
       <c r="B94" t="n">
-        <v>-0.001330173434265457</v>
+        <v>-0.005486940308738251</v>
       </c>
       <c r="C94" t="n">
-        <v>-0.001182040302227304</v>
+        <v>-6.333614990798195e-05</v>
       </c>
       <c r="D94" t="n">
-        <v>-0.001256106868246381</v>
+        <v>-0.002775138229323116</v>
       </c>
     </row>
     <row r="95">
@@ -1758,13 +1758,13 @@
         <v>44165</v>
       </c>
       <c r="B95" t="n">
-        <v>0</v>
+        <v>0.01230990250216194</v>
       </c>
       <c r="C95" t="n">
-        <v>0</v>
+        <v>0.02445008862786915</v>
       </c>
       <c r="D95" t="n">
-        <v>0</v>
+        <v>0.01837999556501554</v>
       </c>
     </row>
     <row r="96">
@@ -1772,13 +1772,13 @@
         <v>44196</v>
       </c>
       <c r="B96" t="n">
-        <v>0</v>
+        <v>0.004063287141380822</v>
       </c>
       <c r="C96" t="n">
-        <v>0</v>
+        <v>0.006576531906913014</v>
       </c>
       <c r="D96" t="n">
-        <v>0</v>
+        <v>0.005319909524146918</v>
       </c>
     </row>
     <row r="97">
@@ -1786,13 +1786,13 @@
         <v>44227</v>
       </c>
       <c r="B97" t="n">
-        <v>-0.0010053074636919</v>
+        <v>0.00161532382764</v>
       </c>
       <c r="C97" t="n">
-        <v>-5.014464644390067e-05</v>
+        <v>0.0003467533375282952</v>
       </c>
       <c r="D97" t="n">
-        <v>-0.0005277260550679002</v>
+        <v>0.0009810385825841474</v>
       </c>
     </row>
     <row r="98">
@@ -1800,13 +1800,13 @@
         <v>44255</v>
       </c>
       <c r="B98" t="n">
-        <v>0</v>
+        <v>0.003534044951564806</v>
       </c>
       <c r="C98" t="n">
-        <v>0</v>
+        <v>0.009250238510884856</v>
       </c>
       <c r="D98" t="n">
-        <v>0</v>
+        <v>0.006392141731224831</v>
       </c>
     </row>
     <row r="99">
@@ -1814,13 +1814,13 @@
         <v>44286</v>
       </c>
       <c r="B99" t="n">
-        <v>0</v>
+        <v>0.005574566270269039</v>
       </c>
       <c r="C99" t="n">
-        <v>0</v>
+        <v>0.003928979200317459</v>
       </c>
       <c r="D99" t="n">
-        <v>0</v>
+        <v>0.004751772735293249</v>
       </c>
     </row>
     <row r="100">
@@ -1828,13 +1828,13 @@
         <v>44316</v>
       </c>
       <c r="B100" t="n">
-        <v>0.0006173270888059436</v>
+        <v>0.001151162892702203</v>
       </c>
       <c r="C100" t="n">
-        <v>0.0003134468668289818</v>
+        <v>0.002972163539489932</v>
       </c>
       <c r="D100" t="n">
-        <v>0.0004653869778174627</v>
+        <v>0.002061663216096068</v>
       </c>
     </row>
     <row r="101">
@@ -1842,13 +1842,13 @@
         <v>44347</v>
       </c>
       <c r="B101" t="n">
-        <v>0</v>
+        <v>0.002256106870285316</v>
       </c>
       <c r="C101" t="n">
-        <v>0</v>
+        <v>0.004995104293865679</v>
       </c>
       <c r="D101" t="n">
-        <v>0</v>
+        <v>0.003625605582075498</v>
       </c>
     </row>
     <row r="102">
@@ -1856,13 +1856,13 @@
         <v>44377</v>
       </c>
       <c r="B102" t="n">
-        <v>0</v>
+        <v>0.001052263658717751</v>
       </c>
       <c r="C102" t="n">
-        <v>0</v>
+        <v>-0.00296797146469415</v>
       </c>
       <c r="D102" t="n">
-        <v>0</v>
+        <v>-0.0009578539029881995</v>
       </c>
     </row>
     <row r="103">
@@ -1870,13 +1870,13 @@
         <v>44408</v>
       </c>
       <c r="B103" t="n">
-        <v>0.0004921419780845548</v>
+        <v>-0.002255855817686995</v>
       </c>
       <c r="C103" t="n">
-        <v>0.0005774829810815729</v>
+        <v>-0.004493434264481605</v>
       </c>
       <c r="D103" t="n">
-        <v>0.0005348124795830639</v>
+        <v>-0.0033746450410843</v>
       </c>
     </row>
     <row r="104">
@@ -1884,13 +1884,13 @@
         <v>44439</v>
       </c>
       <c r="B104" t="n">
-        <v>0</v>
+        <v>0.004644203020161863</v>
       </c>
       <c r="C104" t="n">
-        <v>0</v>
+        <v>0.002292892284528291</v>
       </c>
       <c r="D104" t="n">
-        <v>0</v>
+        <v>0.003468547652345077</v>
       </c>
     </row>
     <row r="105">
@@ -1898,13 +1898,13 @@
         <v>44469</v>
       </c>
       <c r="B105" t="n">
-        <v>0</v>
+        <v>-0.00400242589246992</v>
       </c>
       <c r="C105" t="n">
-        <v>0</v>
+        <v>-0.001337972590039114</v>
       </c>
       <c r="D105" t="n">
-        <v>0</v>
+        <v>-0.002670199241254517</v>
       </c>
     </row>
     <row r="106">
@@ -1912,13 +1912,13 @@
         <v>44500</v>
       </c>
       <c r="B106" t="n">
-        <v>0.00300497739077275</v>
+        <v>0.004832407029971543</v>
       </c>
       <c r="C106" t="n">
-        <v>0.0003984730773927931</v>
+        <v>-0.004016955306211486</v>
       </c>
       <c r="D106" t="n">
-        <v>0.001701725234082771</v>
+        <v>0.0004077258618800286</v>
       </c>
     </row>
     <row r="107">
@@ -1926,13 +1926,13 @@
         <v>44530</v>
       </c>
       <c r="B107" t="n">
-        <v>0</v>
+        <v>-0.0006323417005649705</v>
       </c>
       <c r="C107" t="n">
-        <v>0</v>
+        <v>-0.008498332196790174</v>
       </c>
       <c r="D107" t="n">
-        <v>0</v>
+        <v>-0.004565336948677572</v>
       </c>
     </row>
     <row r="108">
@@ -1940,13 +1940,13 @@
         <v>44561</v>
       </c>
       <c r="B108" t="n">
-        <v>0</v>
+        <v>0.006018763999976469</v>
       </c>
       <c r="C108" t="n">
-        <v>0</v>
+        <v>0.007946620240895786</v>
       </c>
       <c r="D108" t="n">
-        <v>0</v>
+        <v>0.006982692120436127</v>
       </c>
     </row>
     <row r="109">
@@ -1954,13 +1954,13 @@
         <v>44592</v>
       </c>
       <c r="B109" t="n">
-        <v>-0.003098065045674139</v>
+        <v>-0.006362819077102753</v>
       </c>
       <c r="C109" t="n">
-        <v>-0.000389819615259498</v>
+        <v>0.0007832127868432548</v>
       </c>
       <c r="D109" t="n">
-        <v>-0.001743942330466818</v>
+        <v>-0.002789803145129749</v>
       </c>
     </row>
     <row r="110">
@@ -1968,13 +1968,13 @@
         <v>44620</v>
       </c>
       <c r="B110" t="n">
-        <v>0</v>
+        <v>-0.001616348007943258</v>
       </c>
       <c r="C110" t="n">
-        <v>0</v>
+        <v>-0.003290187052578196</v>
       </c>
       <c r="D110" t="n">
-        <v>0</v>
+        <v>-0.002453267530260727</v>
       </c>
     </row>
     <row r="111">
@@ -1982,13 +1982,13 @@
         <v>44651</v>
       </c>
       <c r="B111" t="n">
-        <v>0</v>
+        <v>0.002606702530988268</v>
       </c>
       <c r="C111" t="n">
-        <v>0</v>
+        <v>0.003898437144320812</v>
       </c>
       <c r="D111" t="n">
-        <v>0</v>
+        <v>0.00325256983765454</v>
       </c>
     </row>
     <row r="112">
@@ -1996,13 +1996,13 @@
         <v>44681</v>
       </c>
       <c r="B112" t="n">
-        <v>-0.001944052455187555</v>
+        <v>-0.007326553816003468</v>
       </c>
       <c r="C112" t="n">
-        <v>-0.0001806722874017188</v>
+        <v>-0.005780865475989291</v>
       </c>
       <c r="D112" t="n">
-        <v>-0.001062362371294637</v>
+        <v>-0.006553709645996379</v>
       </c>
     </row>
     <row r="113">
@@ -2010,13 +2010,13 @@
         <v>44712</v>
       </c>
       <c r="B113" t="n">
-        <v>0</v>
+        <v>0.002969861838923372</v>
       </c>
       <c r="C113" t="n">
-        <v>0</v>
+        <v>-0.0001034601589355613</v>
       </c>
       <c r="D113" t="n">
-        <v>0</v>
+        <v>0.001433200839993905</v>
       </c>
     </row>
     <row r="114">
@@ -2024,13 +2024,13 @@
         <v>44742</v>
       </c>
       <c r="B114" t="n">
-        <v>0</v>
+        <v>-0.01153018462491404</v>
       </c>
       <c r="C114" t="n">
-        <v>0</v>
+        <v>-0.01191455718393305</v>
       </c>
       <c r="D114" t="n">
-        <v>0</v>
+        <v>-0.01172237090442355</v>
       </c>
     </row>
     <row r="115">
@@ -2038,13 +2038,13 @@
         <v>44773</v>
       </c>
       <c r="B115" t="n">
-        <v>0.001929123887692443</v>
+        <v>0.01244050936113175</v>
       </c>
       <c r="C115" t="n">
-        <v>0.002798522168519712</v>
+        <v>0.008710308530308544</v>
       </c>
       <c r="D115" t="n">
-        <v>0.002363823028106078</v>
+        <v>0.01057540894572015</v>
       </c>
     </row>
     <row r="116">
@@ -2052,13 +2052,13 @@
         <v>44804</v>
       </c>
       <c r="B116" t="n">
-        <v>0</v>
+        <v>-0.001179775651768718</v>
       </c>
       <c r="C116" t="n">
-        <v>0</v>
+        <v>-0.005313859008484269</v>
       </c>
       <c r="D116" t="n">
-        <v>0</v>
+        <v>-0.003246817330126493</v>
       </c>
     </row>
     <row r="117">
@@ -2066,13 +2066,13 @@
         <v>44834</v>
       </c>
       <c r="B117" t="n">
-        <v>0</v>
+        <v>-0.01014934892678825</v>
       </c>
       <c r="C117" t="n">
-        <v>0</v>
+        <v>-0.006446491652426369</v>
       </c>
       <c r="D117" t="n">
-        <v>0</v>
+        <v>-0.008297920289607307</v>
       </c>
     </row>
     <row r="118">
@@ -2080,13 +2080,13 @@
         <v>44865</v>
       </c>
       <c r="B118" t="n">
-        <v>0.003104691741410518</v>
+        <v>0.01967609003376033</v>
       </c>
       <c r="C118" t="n">
-        <v>0.003905384233627787</v>
+        <v>0.01166994002633051</v>
       </c>
       <c r="D118" t="n">
-        <v>0.003505037987519152</v>
+        <v>0.01567301503004542</v>
       </c>
     </row>
     <row r="119">
@@ -2094,13 +2094,13 @@
         <v>44895</v>
       </c>
       <c r="B119" t="n">
-        <v>0</v>
+        <v>0.009353635622181767</v>
       </c>
       <c r="C119" t="n">
-        <v>0</v>
+        <v>0.01447259285033423</v>
       </c>
       <c r="D119" t="n">
-        <v>0</v>
+        <v>0.011913114236258</v>
       </c>
     </row>
     <row r="120">
@@ -2108,13 +2108,13 @@
         <v>44926</v>
       </c>
       <c r="B120" t="n">
-        <v>0</v>
+        <v>-0.006386808191654871</v>
       </c>
       <c r="C120" t="n">
-        <v>0</v>
+        <v>0.002171602084345877</v>
       </c>
       <c r="D120" t="n">
-        <v>0</v>
+        <v>-0.002107603053654497</v>
       </c>
     </row>
     <row r="121">
@@ -2122,13 +2122,13 @@
         <v>44957</v>
       </c>
       <c r="B121" t="n">
-        <v>0.001706604242108286</v>
+        <v>0.01476733241993595</v>
       </c>
       <c r="C121" t="n">
-        <v>0.004213906312306737</v>
+        <v>0.01221465871207589</v>
       </c>
       <c r="D121" t="n">
-        <v>0.002960255277207511</v>
+        <v>0.01349099556600592</v>
       </c>
     </row>
     <row r="122">
@@ -2136,13 +2136,13 @@
         <v>44985</v>
       </c>
       <c r="B122" t="n">
-        <v>0</v>
+        <v>-0.003090648816935946</v>
       </c>
       <c r="C122" t="n">
-        <v>0</v>
+        <v>-7.848319823005619e-05</v>
       </c>
       <c r="D122" t="n">
-        <v>0</v>
+        <v>-0.001584566007583001</v>
       </c>
     </row>
     <row r="123">
@@ -2150,13 +2150,13 @@
         <v>45016</v>
       </c>
       <c r="B123" t="n">
-        <v>0</v>
+        <v>-0.0007693303121859461</v>
       </c>
       <c r="C123" t="n">
-        <v>0</v>
+        <v>0.0004537386839608398</v>
       </c>
       <c r="D123" t="n">
-        <v>0</v>
+        <v>-0.0001577958141125531</v>
       </c>
     </row>
     <row r="124">
@@ -2164,13 +2164,13 @@
         <v>45046</v>
       </c>
       <c r="B124" t="n">
-        <v>0.0004167216084569291</v>
+        <v>-0.002882834408604159</v>
       </c>
       <c r="C124" t="n">
-        <v>0.001378382975079839</v>
+        <v>0.0005118172765187319</v>
       </c>
       <c r="D124" t="n">
-        <v>0.0008975522917683841</v>
+        <v>-0.001185508566042713</v>
       </c>
     </row>
     <row r="125">
@@ -2178,13 +2178,13 @@
         <v>45077</v>
       </c>
       <c r="B125" t="n">
-        <v>0</v>
+        <v>-0.0007196821403894497</v>
       </c>
       <c r="C125" t="n">
-        <v>0</v>
+        <v>-0.003816191793443763</v>
       </c>
       <c r="D125" t="n">
-        <v>0</v>
+        <v>-0.002267936966916607</v>
       </c>
     </row>
     <row r="126">
@@ -2192,13 +2192,13 @@
         <v>45107</v>
       </c>
       <c r="B126" t="n">
-        <v>0</v>
+        <v>0.007858145941650159</v>
       </c>
       <c r="C126" t="n">
-        <v>0</v>
+        <v>0.004564606131257406</v>
       </c>
       <c r="D126" t="n">
-        <v>0</v>
+        <v>0.006211376036453782</v>
       </c>
     </row>
     <row r="127">
@@ -2206,13 +2206,13 @@
         <v>45138</v>
       </c>
       <c r="B127" t="n">
-        <v>0.0003411730941684068</v>
+        <v>0.004054584524105001</v>
       </c>
       <c r="C127" t="n">
-        <v>0.001520653136856899</v>
+        <v>0.006030046502432192</v>
       </c>
       <c r="D127" t="n">
-        <v>0.0009309131155126528</v>
+        <v>0.005042315513268596</v>
       </c>
     </row>
     <row r="128">
@@ -2220,13 +2220,13 @@
         <v>45169</v>
       </c>
       <c r="B128" t="n">
-        <v>0</v>
+        <v>-0.0002425467269705773</v>
       </c>
       <c r="C128" t="n">
-        <v>0</v>
+        <v>-0.005326371289108664</v>
       </c>
       <c r="D128" t="n">
-        <v>0</v>
+        <v>-0.002784459008039621</v>
       </c>
     </row>
     <row r="129">
@@ -2234,13 +2234,13 @@
         <v>45199</v>
       </c>
       <c r="B129" t="n">
-        <v>0</v>
+        <v>-0.005637567342307405</v>
       </c>
       <c r="C129" t="n">
-        <v>0</v>
+        <v>-0.006371588464255702</v>
       </c>
       <c r="D129" t="n">
-        <v>0</v>
+        <v>-0.006004577903281553</v>
       </c>
     </row>
     <row r="130">
@@ -2248,13 +2248,13 @@
         <v>45230</v>
       </c>
       <c r="B130" t="n">
-        <v>-0.000634379408391366</v>
+        <v>-0.008892321755265527</v>
       </c>
       <c r="C130" t="n">
-        <v>-0.003582847811618604</v>
+        <v>-0.008583342823445759</v>
       </c>
       <c r="D130" t="n">
-        <v>-0.002108613610004985</v>
+        <v>-0.008737832289355643</v>
       </c>
     </row>
     <row r="131">
@@ -2262,13 +2262,13 @@
         <v>45260</v>
       </c>
       <c r="B131" t="n">
-        <v>0.0009535739971629335</v>
+        <v>0.01041568024202425</v>
       </c>
       <c r="C131" t="n">
-        <v>0</v>
+        <v>0.01243099228202686</v>
       </c>
       <c r="D131" t="n">
-        <v>0.0004767869985814667</v>
+        <v>0.01142333626202555</v>
       </c>
     </row>
     <row r="132">
@@ -2276,13 +2276,13 @@
         <v>45291</v>
       </c>
       <c r="B132" t="n">
-        <v>0.008254904180706468</v>
+        <v>0.006730202375647817</v>
       </c>
       <c r="C132" t="n">
         <v>0</v>
       </c>
       <c r="D132" t="n">
-        <v>0.004127452090353234</v>
+        <v>0.003365101187823908</v>
       </c>
     </row>
     <row r="133">
@@ -2290,13 +2290,13 @@
         <v>45322</v>
       </c>
       <c r="B133" t="n">
-        <v>0.001127186744428554</v>
+        <v>0.0002637239995576069</v>
       </c>
       <c r="C133" t="n">
         <v>0</v>
       </c>
       <c r="D133" t="n">
-        <v>0.0005635933722142772</v>
+        <v>0.0001318619997788035</v>
       </c>
     </row>
     <row r="134">
@@ -2304,13 +2304,13 @@
         <v>45351</v>
       </c>
       <c r="B134" t="n">
-        <v>0</v>
+        <v>0.003130083661216129</v>
       </c>
       <c r="C134" t="n">
         <v>0</v>
       </c>
       <c r="D134" t="n">
-        <v>0</v>
+        <v>0.001565041830608065</v>
       </c>
     </row>
     <row r="135">
@@ -2318,13 +2318,13 @@
         <v>45382</v>
       </c>
       <c r="B135" t="n">
-        <v>0</v>
+        <v>0.00517241024257291</v>
       </c>
       <c r="C135" t="n">
         <v>0</v>
       </c>
       <c r="D135" t="n">
-        <v>0</v>
+        <v>0.002586205121286455</v>
       </c>
     </row>
     <row r="136">
@@ -2332,13 +2332,13 @@
         <v>45412</v>
       </c>
       <c r="B136" t="n">
-        <v>-0.001972247155172881</v>
+        <v>-0.007717175567007514</v>
       </c>
       <c r="C136" t="n">
         <v>0</v>
       </c>
       <c r="D136" t="n">
-        <v>-0.0009861235775864403</v>
+        <v>-0.003858587783503757</v>
       </c>
     </row>
     <row r="137">
@@ -2346,13 +2346,13 @@
         <v>45443</v>
       </c>
       <c r="B137" t="n">
-        <v>0</v>
+        <v>0.003148042503455632</v>
       </c>
       <c r="C137" t="n">
         <v>0</v>
       </c>
       <c r="D137" t="n">
-        <v>0</v>
+        <v>0.001574021251727816</v>
       </c>
     </row>
     <row r="138">
@@ -2360,13 +2360,13 @@
         <v>45473</v>
       </c>
       <c r="B138" t="n">
-        <v>0</v>
+        <v>0.0008419479803182922</v>
       </c>
       <c r="C138" t="n">
         <v>0</v>
       </c>
       <c r="D138" t="n">
-        <v>0</v>
+        <v>0.0004209739901591461</v>
       </c>
     </row>
     <row r="139">
@@ -2374,13 +2374,13 @@
         <v>45504</v>
       </c>
       <c r="B139" t="n">
-        <v>0.0003172064949014521</v>
+        <v>-0.001576180583427471</v>
       </c>
       <c r="C139" t="n">
         <v>0</v>
       </c>
       <c r="D139" t="n">
-        <v>0.0001586032474507261</v>
+        <v>-0.0007880902917137354</v>
       </c>
     </row>
     <row r="140">
@@ -2388,13 +2388,13 @@
         <v>45535</v>
       </c>
       <c r="B140" t="n">
-        <v>0</v>
+        <v>0.003377861107593245</v>
       </c>
       <c r="C140" t="n">
-        <v>0</v>
+        <v>0.003962274581607119</v>
       </c>
       <c r="D140" t="n">
-        <v>0</v>
+        <v>0.003670067844600182</v>
       </c>
     </row>
     <row r="141">
@@ -2402,13 +2402,13 @@
         <v>45565</v>
       </c>
       <c r="B141" t="n">
-        <v>0</v>
+        <v>0.00265349493303426</v>
       </c>
       <c r="C141" t="n">
-        <v>0</v>
+        <v>0.002743296265254473</v>
       </c>
       <c r="D141" t="n">
-        <v>0</v>
+        <v>0.002698395599144366</v>
       </c>
     </row>
     <row r="142">
@@ -2416,13 +2416,13 @@
         <v>45596</v>
       </c>
       <c r="B142" t="n">
-        <v>-0.0005633191371028033</v>
+        <v>-0.002479312670459903</v>
       </c>
       <c r="C142" t="n">
-        <v>-0.005178514647916862</v>
+        <v>-0.003929496358284581</v>
       </c>
       <c r="D142" t="n">
-        <v>-0.002870916892509833</v>
+        <v>-0.003204404514372242</v>
       </c>
     </row>
     <row r="143">
@@ -2430,13 +2430,13 @@
         <v>45626</v>
       </c>
       <c r="B143" t="n">
-        <v>0</v>
+        <v>0.002516259175896956</v>
       </c>
       <c r="C143" t="n">
-        <v>0</v>
+        <v>-0.001493295861636263</v>
       </c>
       <c r="D143" t="n">
-        <v>0</v>
+        <v>0.0005114816571303463</v>
       </c>
     </row>
     <row r="144">
@@ -2444,13 +2444,13 @@
         <v>45657</v>
       </c>
       <c r="B144" t="n">
-        <v>0</v>
+        <v>-0.00437373831068303</v>
       </c>
       <c r="C144" t="n">
-        <v>0</v>
+        <v>-0.001952123872780049</v>
       </c>
       <c r="D144" t="n">
-        <v>0</v>
+        <v>-0.003162931091731539</v>
       </c>
     </row>
     <row r="145">
@@ -2458,13 +2458,13 @@
         <v>45688</v>
       </c>
       <c r="B145" t="n">
-        <v>-0.003914188890215721</v>
+        <v>0.003196424444999742</v>
       </c>
       <c r="C145" t="n">
-        <v>0.003738133358179611</v>
+        <v>0.004984273704892115</v>
       </c>
       <c r="D145" t="n">
-        <v>-8.802776601805505e-05</v>
+        <v>0.004090349074945928</v>
       </c>
     </row>
     <row r="146">
@@ -2472,13 +2472,13 @@
         <v>45716</v>
       </c>
       <c r="B146" t="n">
-        <v>0</v>
+        <v>-0.003645626092250158</v>
       </c>
       <c r="C146" t="n">
-        <v>0</v>
+        <v>0.00486420351692811</v>
       </c>
       <c r="D146" t="n">
-        <v>0</v>
+        <v>0.0006092887123389757</v>
       </c>
     </row>
     <row r="147">
@@ -2486,13 +2486,13 @@
         <v>45747</v>
       </c>
       <c r="B147" t="n">
-        <v>0</v>
+        <v>-0.004001332191781196</v>
       </c>
       <c r="C147" t="n">
-        <v>0</v>
+        <v>0.0003758952212852942</v>
       </c>
       <c r="D147" t="n">
-        <v>0</v>
+        <v>-0.001812718485247951</v>
       </c>
     </row>
   </sheetData>
